--- a/dados_all_stores/Keys Summary - All Stores (Stores) (2026-08-27).xlsx
+++ b/dados_all_stores/Keys Summary - All Stores (Stores) (2026-08-27).xlsx
@@ -912,33 +912,33 @@
   </si>
   <si>
     <t>214
-184</t>
-  </si>
-  <si>
-    <t>20</t>
-  </si>
-  <si>
-    <t>R$ 847.781,31</t>
-  </si>
-  <si>
-    <t>R$ 4.370,01
-R$ 4.435,97</t>
-  </si>
-  <si>
-    <t>(2.3%)
+187</t>
+  </si>
+  <si>
+    <t>17</t>
+  </si>
+  <si>
+    <t>R$ 856.772,37</t>
+  </si>
+  <si>
+    <t>R$ 4.349,10
+R$ 4.412,88</t>
+  </si>
+  <si>
+    <t>(2.4%)
 (0.9%)</t>
   </si>
   <si>
-    <t>47.4</t>
-  </si>
-  <si>
-    <t>(8.6%)</t>
-  </si>
-  <si>
-    <t>(44.3%)</t>
-  </si>
-  <si>
-    <t>(82.8%)</t>
+    <t>47.2</t>
+  </si>
+  <si>
+    <t>(8.5%)</t>
+  </si>
+  <si>
+    <t>(42.1%)</t>
+  </si>
+  <si>
+    <t>(80.5%)</t>
   </si>
   <si>
     <t>3.9%</t>
@@ -947,34 +947,34 @@
     <t>0.4%</t>
   </si>
   <si>
-    <t>26.2</t>
-  </si>
-  <si>
-    <t>72.3%</t>
-  </si>
-  <si>
-    <t>9.3%</t>
+    <t>26.3</t>
+  </si>
+  <si>
+    <t>72.5%</t>
+  </si>
+  <si>
+    <t>9.4%</t>
   </si>
   <si>
     <t>4.6</t>
   </si>
   <si>
-    <t>7.1</t>
-  </si>
-  <si>
-    <t>11.7</t>
-  </si>
-  <si>
-    <t>18.0</t>
-  </si>
-  <si>
-    <t>73.5%</t>
+    <t>7.2</t>
+  </si>
+  <si>
+    <t>11.8</t>
+  </si>
+  <si>
+    <t>18.1</t>
+  </si>
+  <si>
+    <t>73.3%</t>
   </si>
   <si>
     <t>-R$ 29.140,35</t>
   </si>
   <si>
-    <t>2.95</t>
+    <t>2.94</t>
   </si>
   <si>
     <t>3.52</t>
@@ -5994,7 +5994,7 @@
         <v>19562</v>
       </c>
       <c r="B36" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C36" s="4">
         <v>44</v>
@@ -6030,25 +6030,61 @@
       <c t="s" r="N36" s="4">
         <v>52</v>
       </c>
-      <c r="O36" s="5"/>
-      <c r="P36" s="5"/>
-      <c r="Q36" s="6"/>
-      <c r="R36" s="7"/>
-      <c r="S36" s="6"/>
-      <c r="T36" s="6"/>
-      <c r="U36" s="6"/>
-      <c r="V36" s="6"/>
-      <c r="W36" s="6"/>
-      <c r="X36" s="8"/>
-      <c r="Y36" s="6"/>
-      <c r="Z36" s="6"/>
-      <c r="AA36" s="8"/>
-      <c r="AB36" s="8"/>
-      <c r="AC36" s="8"/>
-      <c r="AD36" s="8"/>
-      <c r="AE36" s="6"/>
+      <c r="O36" s="5">
+        <v>3749.8800000000001</v>
+      </c>
+      <c r="P36" s="5">
+        <v>3749.8800000000001</v>
+      </c>
+      <c r="Q36" s="6">
+        <v>0.1036719605373142</v>
+      </c>
+      <c r="R36" s="7">
+        <v>51</v>
+      </c>
+      <c r="S36" s="6">
+        <v>0.54545454545454541</v>
+      </c>
+      <c r="T36" s="6">
+        <v>0.3367571228945993</v>
+      </c>
+      <c r="U36" s="6">
+        <v>-0.00061367297086840119</v>
+      </c>
+      <c r="V36" s="6">
+        <v>0.11487727607283434</v>
+      </c>
+      <c r="W36" s="6">
+        <v>0.059070156911687842</v>
+      </c>
+      <c r="X36" s="8">
+        <v>33.635832499999999</v>
+      </c>
+      <c r="Y36" s="6">
+        <v>1</v>
+      </c>
+      <c r="Z36" s="6">
+        <v>0.29999999999999999</v>
+      </c>
+      <c r="AA36" s="8">
+        <v>5.8785249999999998</v>
+      </c>
+      <c r="AB36" s="8">
+        <v>12.030769230769231</v>
+      </c>
+      <c r="AC36" s="8">
+        <v>18.316602</v>
+      </c>
+      <c r="AD36" s="8">
+        <v>24.922082499999998</v>
+      </c>
+      <c r="AE36" s="6">
+        <v>0.57499999999999996</v>
+      </c>
       <c r="AF36" s="9"/>
-      <c r="AG36" s="5"/>
+      <c r="AG36" s="5">
+        <v>0</v>
+      </c>
       <c r="AH36" s="10">
         <v>4</v>
       </c>
@@ -7915,7 +7951,7 @@
         <v>19602</v>
       </c>
       <c r="B51" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C51" s="4">
         <v>44</v>
@@ -7951,25 +7987,61 @@
       <c t="s" r="N51" s="4">
         <v>52</v>
       </c>
-      <c r="O51" s="5"/>
-      <c r="P51" s="5"/>
-      <c r="Q51" s="6"/>
-      <c r="R51" s="7"/>
-      <c r="S51" s="6"/>
-      <c r="T51" s="6"/>
-      <c r="U51" s="6"/>
-      <c r="V51" s="6"/>
-      <c r="W51" s="6"/>
-      <c r="X51" s="8"/>
-      <c r="Y51" s="6"/>
-      <c r="Z51" s="6"/>
-      <c r="AA51" s="8"/>
-      <c r="AB51" s="8"/>
-      <c r="AC51" s="8"/>
-      <c r="AD51" s="8"/>
-      <c r="AE51" s="6"/>
+      <c r="O51" s="5">
+        <v>533.39999999999998</v>
+      </c>
+      <c r="P51" s="5">
+        <v>533.39999999999998</v>
+      </c>
+      <c r="Q51" s="6">
+        <v>0.40375809253118566</v>
+      </c>
+      <c r="R51" s="7">
+        <v>5</v>
+      </c>
+      <c r="S51" s="6">
+        <v>0.25</v>
+      </c>
+      <c r="T51" s="6">
+        <v>0</v>
+      </c>
+      <c r="U51" s="6">
+        <v>-0.3355643044619423</v>
+      </c>
+      <c r="V51" s="6">
+        <v>0.036439820022497189</v>
+      </c>
+      <c r="W51" s="6">
+        <v>-0.20354893138357705</v>
+      </c>
+      <c r="X51" s="8">
+        <v>23.261099999999999</v>
+      </c>
+      <c r="Y51" s="6">
+        <v>1</v>
+      </c>
+      <c r="Z51" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA51" s="8">
+        <v>4.96</v>
+      </c>
+      <c r="AB51" s="8">
+        <v>8.8389000000000006</v>
+      </c>
+      <c r="AC51" s="8">
+        <v>12.433332</v>
+      </c>
+      <c r="AD51" s="8">
+        <v>19.344433333333331</v>
+      </c>
+      <c r="AE51" s="6">
+        <v>1</v>
+      </c>
       <c r="AF51" s="9"/>
-      <c r="AG51" s="5"/>
+      <c r="AG51" s="5">
+        <v>0</v>
+      </c>
       <c r="AH51" s="10">
         <v>2</v>
       </c>
@@ -12674,7 +12746,7 @@
         <v>0</v>
       </c>
       <c r="AH88" s="10">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AI88" s="11"/>
       <c r="AJ88" s="13">
@@ -12713,7 +12785,7 @@
         <v>19693</v>
       </c>
       <c r="B89" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C89" s="4">
         <v>44</v>
@@ -12747,25 +12819,59 @@
       <c t="s" r="N89" s="4">
         <v>52</v>
       </c>
-      <c r="O89" s="5"/>
-      <c r="P89" s="5"/>
-      <c r="Q89" s="6"/>
-      <c r="R89" s="7"/>
-      <c r="S89" s="6"/>
-      <c r="T89" s="6"/>
-      <c r="U89" s="6"/>
-      <c r="V89" s="6"/>
-      <c r="W89" s="6"/>
-      <c r="X89" s="8"/>
-      <c r="Y89" s="6"/>
-      <c r="Z89" s="6"/>
-      <c r="AA89" s="8"/>
-      <c r="AB89" s="8"/>
+      <c r="O89" s="5">
+        <v>4707.7799999999997</v>
+      </c>
+      <c r="P89" s="5">
+        <v>4707.7799999999997</v>
+      </c>
+      <c r="Q89" s="6">
+        <v>-0.19063026510332504</v>
+      </c>
+      <c r="R89" s="7">
+        <v>50</v>
+      </c>
+      <c r="S89" s="6">
+        <v>-0.27536231884057971</v>
+      </c>
+      <c r="T89" s="6">
+        <v>2.9412386730051105</v>
+      </c>
+      <c r="U89" s="6">
+        <v>2.6194967904192636</v>
+      </c>
+      <c r="V89" s="6">
+        <v>0.019053248027732818</v>
+      </c>
+      <c r="W89" s="6">
+        <v>-0.0031291819073958429</v>
+      </c>
+      <c r="X89" s="8">
+        <v>31.111904761904764</v>
+      </c>
+      <c r="Y89" s="6">
+        <v>0.80952380952380953</v>
+      </c>
+      <c r="Z89" s="6">
+        <v>0.19047619047619047</v>
+      </c>
+      <c r="AA89" s="8">
+        <v>5.0135416666666668</v>
+      </c>
+      <c r="AB89" s="8">
+        <v>7.6142857142857148</v>
+      </c>
       <c r="AC89" s="8"/>
-      <c r="AD89" s="8"/>
-      <c r="AE89" s="6"/>
+      <c r="AD89" s="8">
+        <v>20.985714285714284</v>
+      </c>
+      <c r="AE89" s="6">
+        <v>0.52380952380952384</v>
+      </c>
       <c r="AF89" s="9"/>
-      <c r="AG89" s="5"/>
+      <c r="AG89" s="5">
+        <v>0</v>
+      </c>
       <c r="AH89" s="10">
         <v>2</v>
       </c>
@@ -16825,7 +16931,7 @@
         <v>-133.80000000000001</v>
       </c>
       <c r="AH121" s="10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI121" s="11"/>
       <c r="AJ121" s="13">
@@ -17087,7 +17193,7 @@
         <v>0</v>
       </c>
       <c r="AH123" s="10">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AI123" s="11"/>
       <c r="AJ123" s="13">
@@ -17480,7 +17586,7 @@
         <v>0</v>
       </c>
       <c r="AH126" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AI126" s="11"/>
       <c r="AJ126" s="13">
@@ -18657,7 +18763,7 @@
         <v>-84.700000000000003</v>
       </c>
       <c r="AH135" s="10">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AI135" s="11"/>
       <c r="AJ135" s="13">
@@ -18788,7 +18894,7 @@
         <v>-378.60000000000002</v>
       </c>
       <c r="AH136" s="10">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AI136" s="11"/>
       <c r="AJ136" s="13">
@@ -20971,7 +21077,7 @@
         <v>-126.09</v>
       </c>
       <c r="AH153" s="10">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AI153" s="11"/>
       <c r="AJ153" s="13">
@@ -21098,7 +21204,7 @@
         <v>185.09999999999999</v>
       </c>
       <c r="AH154" s="10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AI154" s="11"/>
       <c r="AJ154" s="13">
@@ -22255,7 +22361,7 @@
         <v>-249.30000000000001</v>
       </c>
       <c r="AH163" s="10">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AI163" s="11"/>
       <c r="AJ163" s="13">
@@ -28422,7 +28528,7 @@
       <c r="AF212" s="9"/>
       <c r="AG212" s="5"/>
       <c r="AH212" s="10">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AI212" s="11"/>
       <c r="AJ212" s="12"/>
